--- a/Result/profitability/1447.xlsx
+++ b/Result/profitability/1447.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.15375</v>
+        <v>-0.13125</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32875</v>
+        <v>1.495</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.145</v>
+        <v>-0.1375</v>
       </c>
       <c r="N3" t="n">
-        <v>1.51625</v>
+        <v>1.725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>-0.19375</v>
       </c>
       <c r="N4" t="n">
-        <v>1.065</v>
+        <v>1.09375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.34</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.48875</v>
+        <v>-0.4225</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.2925</v>
+        <v>-3.912500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3912499999999999</v>
+        <v>-0.37375</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.29</v>
+        <v>-2.94</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.30875</v>
+        <v>-0.26125</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8775</v>
+        <v>-1.76625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2024999999999999</v>
+        <v>-0.2125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9262500000000005</v>
+        <v>-0.9487500000000004</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07624999999999996</v>
+        <v>-0.07624999999999998</v>
       </c>
       <c r="N10" t="n">
         <v>0.2949999999999997</v>
@@ -1772,10 +1772,10 @@
         <v>0.27</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03124999999999996</v>
+        <v>-0.03124999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6999999999999997</v>
+        <v>0.6999999999999996</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.18</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04500000000000003</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>1.305</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7996</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7798</v>
+      </c>
+      <c r="E75" t="n">
+        <v>198</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>55</v>
+      </c>
+      <c r="J75" t="n">
+        <v>42</v>
+      </c>
+      <c r="K75" t="n">
+        <v>15</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.13125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.2575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1800000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06766917293233088</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.03921568627451</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-5.428571428571428</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
